--- a/data/trans_orig/P22_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P22_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el Seguro Sanitario del que es beneficiario en 2007</t>
+          <t>Población según el Seguro Sanitario del que es beneficiaria en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1924</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35243</t>
+          <t>34252</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26608</t>
+          <t>25442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28037</t>
+          <t>29271</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53740</t>
+          <t>55140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35676</t>
+          <t>35486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22197</t>
+          <t>21749</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44178</t>
+          <t>43275</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41599</t>
+          <t>41752</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71748</t>
+          <t>70999</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>628858</t>
+          <t>628447</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>655898</t>
+          <t>655720</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>624209</t>
+          <t>625756</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>651552</t>
+          <t>651892</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1262722</t>
+          <t>1263268</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1300604</t>
+          <t>1300586</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14434</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>42138</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74916</t>
+          <t>73537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27578</t>
+          <t>27797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53011</t>
+          <t>53653</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77551</t>
+          <t>78215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117992</t>
+          <t>118099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>20171</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41349</t>
+          <t>42021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27704</t>
+          <t>27727</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>53553</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53141</t>
+          <t>51902</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87313</t>
+          <t>86678</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>850101</t>
+          <t>849407</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>888241</t>
+          <t>889114</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>870635</t>
+          <t>869668</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>905326</t>
+          <t>905836</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1731159</t>
+          <t>1730662</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1781647</t>
+          <t>1784779</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,62 +1906,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1884</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>7501</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1645</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>8219</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73690</t>
+          <t>73013</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30575</t>
+          <t>31512</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57329</t>
+          <t>55177</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>80502</t>
+          <t>81351</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>120724</t>
+          <t>121109</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17197</t>
+          <t>18146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39839</t>
+          <t>40012</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22861</t>
+          <t>22628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44693</t>
+          <t>43971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45882</t>
+          <t>45164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76645</t>
+          <t>75836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>571573</t>
+          <t>570245</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>608605</t>
+          <t>608037</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>592474</t>
+          <t>592587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>623745</t>
+          <t>625307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1175962</t>
+          <t>1174184</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1222961</t>
+          <t>1223906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,9%</t>
         </is>
       </c>
     </row>
@@ -2440,82 +2440,82 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>931</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4663</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61976</t>
+          <t>63461</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94890</t>
+          <t>93550</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61924</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97218</t>
+          <t>96745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>133515</t>
+          <t>130610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>179648</t>
+          <t>177867</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37615</t>
+          <t>38033</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>66085</t>
+          <t>64872</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32334</t>
+          <t>31848</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59091</t>
+          <t>59554</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>76403</t>
+          <t>75237</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>113187</t>
+          <t>113229</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>791982</t>
+          <t>791928</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>831235</t>
+          <t>830622</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>894375</t>
+          <t>892630</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>935386</t>
+          <t>935180</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1695745</t>
+          <t>1700973</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1753981</t>
+          <t>1758645</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14932</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>190297</t>
+          <t>187060</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>244673</t>
+          <t>246072</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>150341</t>
+          <t>152130</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203698</t>
+          <t>204233</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>356281</t>
+          <t>351145</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>434063</t>
+          <t>431657</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>109568</t>
+          <t>109849</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154560</t>
+          <t>154994</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,82 +3250,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>146110</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>123197</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>170664</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>276878</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>246468</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>314462</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>4,73%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>146110</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>123093</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>169825</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>276878</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>245164</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>311616</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2880886</t>
+          <t>2883107</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2950648</t>
+          <t>2952586</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3017647</t>
+          <t>3017994</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3084749</t>
+          <t>3085285</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5919098</t>
+          <t>5922062</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6018233</t>
+          <t>6023059</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el Seguro Sanitario del que es beneficiario en 2012</t>
+          <t>Población según el Seguro Sanitario del que es beneficiaria en 2012 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,97 +3810,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2056</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35111</t>
+          <t>34749</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29811</t>
+          <t>29864</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30200</t>
+          <t>30461</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57341</t>
+          <t>56844</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15995</t>
+          <t>15911</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39805</t>
+          <t>39617</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>15564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21748</t>
+          <t>21980</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49043</t>
+          <t>48026</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>637945</t>
+          <t>639635</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>668845</t>
+          <t>667654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>658506</t>
+          <t>658347</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>679076</t>
+          <t>679354</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1304949</t>
+          <t>1305008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1342625</t>
+          <t>1341330</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -4379,97 +4379,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2086</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>6581</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>1196</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5999</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>6361</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1196</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>6726</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30298</t>
+          <t>29436</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55703</t>
+          <t>55291</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26235</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52279</t>
+          <t>52326</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62146</t>
+          <t>62576</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97610</t>
+          <t>99244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33410</t>
+          <t>34413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65383</t>
+          <t>67204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14963</t>
+          <t>15147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34097</t>
+          <t>36155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53787</t>
+          <t>53941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92831</t>
+          <t>91860</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>907170</t>
+          <t>904769</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>947091</t>
+          <t>944920</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>952763</t>
+          <t>951634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>983922</t>
+          <t>984402</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1870628</t>
+          <t>1871160</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1921762</t>
+          <t>1921388</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,47 +4983,47 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2444</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2114</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2444</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27253</t>
+          <t>29081</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54850</t>
+          <t>55354</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>20471</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43872</t>
+          <t>42813</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>53519</t>
+          <t>53147</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>89456</t>
+          <t>88777</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26246</t>
+          <t>28236</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55373</t>
+          <t>57628</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31306</t>
+          <t>30472</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60967</t>
+          <t>61755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66319</t>
+          <t>65914</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109689</t>
+          <t>106097</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>655093</t>
+          <t>653308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>693838</t>
+          <t>691274</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>683796</t>
+          <t>682912</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720727</t>
+          <t>720802</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1349437</t>
+          <t>1348704</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401958</t>
+          <t>1402251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,47 +5552,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1268</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39049</t>
+          <t>38143</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67626</t>
+          <t>68441</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47727</t>
+          <t>49775</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80349</t>
+          <t>79733</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94546</t>
+          <t>94309</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137930</t>
+          <t>136652</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33704</t>
+          <t>33671</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61306</t>
+          <t>61972</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34722</t>
+          <t>34276</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62561</t>
+          <t>63515</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>74036</t>
+          <t>74811</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>112753</t>
+          <t>115748</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>827756</t>
+          <t>825833</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>865979</t>
+          <t>866098</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>920050</t>
+          <t>919421</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>961884</t>
+          <t>960666</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1760952</t>
+          <t>1761246</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1816124</t>
+          <t>1820076</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>11066</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12286</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132110</t>
+          <t>133276</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>182600</t>
+          <t>184942</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>125735</t>
+          <t>123817</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>177734</t>
+          <t>179107</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>272919</t>
+          <t>272489</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>347446</t>
+          <t>344341</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>134628</t>
+          <t>132254</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>189833</t>
+          <t>186562</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>100516</t>
+          <t>98361</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148460</t>
+          <t>148153</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>246722</t>
+          <t>245064</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>315779</t>
+          <t>316904</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3065564</t>
+          <t>3066908</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3140029</t>
+          <t>3142409</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3249954</t>
+          <t>3243288</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3315563</t>
+          <t>3315940</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6339294</t>
+          <t>6337181</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6438933</t>
+          <t>6438399</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el Seguro Sanitario del que es beneficiario en 2016</t>
+          <t>Población según el Seguro Sanitario del que es beneficiaria en 2016 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,97 +6887,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4297</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>851</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4628</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4833</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4269</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24305</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>17551</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>39543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31291</t>
+          <t>31652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16389</t>
+          <t>16219</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17829</t>
+          <t>18378</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41211</t>
+          <t>41775</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>628454</t>
+          <t>628708</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>652417</t>
+          <t>651928</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,82 +7241,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>96,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>648186</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>637148</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>657450</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1290283</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>1272470</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>1304110</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>95,83%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>96,85%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>648186</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>636641</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>656861</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>96,34%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>94,62%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1290283</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1274199</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1304365</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>94,63%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26664</t>
+          <t>25741</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53083</t>
+          <t>52086</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34977</t>
+          <t>34825</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62967</t>
+          <t>62736</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67312</t>
+          <t>66800</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107906</t>
+          <t>105909</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40421</t>
+          <t>41166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71329</t>
+          <t>74392</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16533</t>
+          <t>16246</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>35827</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62370</t>
+          <t>61932</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97609</t>
+          <t>100846</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>907475</t>
+          <t>905531</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>945072</t>
+          <t>946763</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>948159</t>
+          <t>949380</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>982398</t>
+          <t>983126</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1866435</t>
+          <t>1864752</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1920390</t>
+          <t>1919658</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -8025,82 +8025,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2090</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7537</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>1083</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5408</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31300</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30019</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>29695</t>
+          <t>29879</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>55771</t>
+          <t>55490</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>10453</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27928</t>
+          <t>27121</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21649</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42860</t>
+          <t>43658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34987</t>
+          <t>34047</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>63073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>707078</t>
+          <t>704942</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>731804</t>
+          <t>730860</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,47 +8379,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>93,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>728897</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>712892</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>741048</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>93,32%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>728897</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>712852</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>741508</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1429907</t>
+          <t>1428240</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1466990</t>
+          <t>1466091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>13059</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40785</t>
+          <t>41841</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68801</t>
+          <t>68766</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54034</t>
+          <t>53659</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89290</t>
+          <t>88740</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101453</t>
+          <t>101543</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145266</t>
+          <t>146432</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>51059</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82089</t>
+          <t>81136</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42632</t>
+          <t>43542</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74621</t>
+          <t>72689</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>101266</t>
+          <t>99015</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>145551</t>
+          <t>143370</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>790109</t>
+          <t>791494</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>831518</t>
+          <t>831811</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>892814</t>
+          <t>894434</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>939859</t>
+          <t>938066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1698147</t>
+          <t>1698761</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1760543</t>
+          <t>1762062</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15345</t>
+          <t>14424</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>850</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18989</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99796</t>
+          <t>100327</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>144998</t>
+          <t>145220</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130487</t>
+          <t>127672</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>180551</t>
+          <t>180542</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>242210</t>
+          <t>242007</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>308062</t>
+          <t>309059</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>132234</t>
+          <t>133439</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>186230</t>
+          <t>183385</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>99097</t>
+          <t>101340</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143996</t>
+          <t>146890</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>246271</t>
+          <t>246904</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>320158</t>
+          <t>310704</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3068828</t>
+          <t>3072144</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3139442</t>
+          <t>3136828</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3224080</t>
+          <t>3222176</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3291989</t>
+          <t>3293097</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6313236</t>
+          <t>6318701</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6407090</t>
+          <t>6408154</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el Seguro Sanitario del que es beneficiario en 2023</t>
+          <t>Población según el Seguro Sanitario del que es beneficiaria en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,62 +9999,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4592</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>864</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4266</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15935</t>
+          <t>16482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36416</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23687</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43209</t>
+          <t>42560</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44476</t>
+          <t>44164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74659</t>
+          <t>71459</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25426</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13796</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33775</t>
+          <t>34849</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>580016</t>
+          <t>580837</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>605005</t>
+          <t>605802</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>672186</t>
+          <t>673129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>695304</t>
+          <t>694110</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1258254</t>
+          <t>1259913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1294331</t>
+          <t>1294749</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45753</t>
+          <t>44515</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121333</t>
+          <t>123386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66272</t>
+          <t>66957</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96207</t>
+          <t>94723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112451</t>
+          <t>107440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201854</t>
+          <t>202854</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47208</t>
+          <t>46395</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20202</t>
+          <t>20415</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37027</t>
+          <t>36961</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>36813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75745</t>
+          <t>75563</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1030596</t>
+          <t>1031001</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1128474</t>
+          <t>1135517</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>832663</t>
+          <t>831030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>865684</t>
+          <t>865450</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1877874</t>
+          <t>1881711</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1996463</t>
+          <t>2005347</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -11102,97 +11102,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4087</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>664</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3572</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3748</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3032</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59143</t>
+          <t>58627</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94376</t>
+          <t>93999</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45316</t>
+          <t>40559</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118782</t>
+          <t>115083</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>105903</t>
+          <t>110139</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>193737</t>
+          <t>196753</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18045</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48530</t>
+          <t>46941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31130</t>
+          <t>31759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29855</t>
+          <t>30563</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66784</t>
+          <t>67486</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>575974</t>
+          <t>577825</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>620411</t>
+          <t>620888</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>788688</t>
+          <t>790518</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>878366</t>
+          <t>882353</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1386977</t>
+          <t>1382888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1503380</t>
+          <t>1492303</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112495</t>
+          <t>110497</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>154765</t>
+          <t>155351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>126498</t>
+          <t>127224</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184773</t>
+          <t>181894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>252081</t>
+          <t>250355</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>322499</t>
+          <t>323132</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31252</t>
+          <t>31546</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>55697</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30837</t>
+          <t>29984</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53771</t>
+          <t>55371</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>67170</t>
+          <t>65657</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>100478</t>
+          <t>99825</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>728443</t>
+          <t>725877</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>775148</t>
+          <t>774954</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>862021</t>
+          <t>865175</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>928024</t>
+          <t>930507</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1605044</t>
+          <t>1607076</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1686427</t>
+          <t>1689238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11698</t>
+          <t>11574</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>251613</t>
+          <t>251315</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>367780</t>
+          <t>367897</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>294517</t>
+          <t>286828</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>401472</t>
+          <t>398720</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>592004</t>
+          <t>593810</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>744476</t>
+          <t>748813</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>88930</t>
+          <t>87735</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>143179</t>
+          <t>143359</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76521</t>
+          <t>77954</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>115608</t>
+          <t>115777</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>178753</t>
+          <t>177030</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>245158</t>
+          <t>248156</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2965753</t>
+          <t>2964842</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3113931</t>
+          <t>3114091</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3197243</t>
+          <t>3200973</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3324693</t>
+          <t>3337930</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6191232</t>
+          <t>6190804</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6384138</t>
+          <t>6384041</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P22_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P22_R-Habitat-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14823</t>
+          <t>15339</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34252</t>
+          <t>35268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25442</t>
+          <t>26548</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29271</t>
+          <t>28664</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55140</t>
+          <t>55144</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16053</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35486</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>21207</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43275</t>
+          <t>43883</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41752</t>
+          <t>41128</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70999</t>
+          <t>72886</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>628447</t>
+          <t>626478</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>655720</t>
+          <t>654900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>625756</t>
+          <t>624353</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>651892</t>
+          <t>652805</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1263268</t>
+          <t>1261648</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1300586</t>
+          <t>1301447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73537</t>
+          <t>73818</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27797</t>
+          <t>29137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53653</t>
+          <t>53966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78215</t>
+          <t>78526</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118099</t>
+          <t>118510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>19581</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42021</t>
+          <t>40624</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27727</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53553</t>
+          <t>52505</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51902</t>
+          <t>52669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86678</t>
+          <t>90060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>849407</t>
+          <t>850709</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>889114</t>
+          <t>887869</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>869668</t>
+          <t>868453</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>905836</t>
+          <t>905116</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1730662</t>
+          <t>1730019</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1784779</t>
+          <t>1783085</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,43%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44067</t>
+          <t>43729</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73013</t>
+          <t>75486</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31512</t>
+          <t>31410</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55177</t>
+          <t>56658</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>81351</t>
+          <t>80552</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>121109</t>
+          <t>121435</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>18230</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40012</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22628</t>
+          <t>21889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43971</t>
+          <t>46439</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>46010</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75836</t>
+          <t>75146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>570245</t>
+          <t>570561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>608037</t>
+          <t>608401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>592587</t>
+          <t>590447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>625307</t>
+          <t>623901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1174184</t>
+          <t>1175292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1223906</t>
+          <t>1222772</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63461</t>
+          <t>63101</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93550</t>
+          <t>95878</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>60789</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>96745</t>
+          <t>94048</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130610</t>
+          <t>133139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>177867</t>
+          <t>177723</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38033</t>
+          <t>37603</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64872</t>
+          <t>65753</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31848</t>
+          <t>31104</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59554</t>
+          <t>56829</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>75237</t>
+          <t>74922</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>113229</t>
+          <t>112588</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>791928</t>
+          <t>788718</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>830622</t>
+          <t>830894</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>892630</t>
+          <t>894219</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>935180</t>
+          <t>935543</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1700973</t>
+          <t>1696490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1758645</t>
+          <t>1754058</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15454</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>17250</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>187060</t>
+          <t>189851</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>246072</t>
+          <t>246640</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>152130</t>
+          <t>152149</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>204233</t>
+          <t>204285</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>351145</t>
+          <t>356337</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>431657</t>
+          <t>429891</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>109849</t>
+          <t>109043</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154994</t>
+          <t>152144</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>123197</t>
+          <t>123070</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>170664</t>
+          <t>170941</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>246468</t>
+          <t>241395</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>314462</t>
+          <t>311429</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2883107</t>
+          <t>2877836</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2952586</t>
+          <t>2952131</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3017994</t>
+          <t>3018120</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3085285</t>
+          <t>3086836</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5922062</t>
+          <t>5919985</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6023059</t>
+          <t>6017928</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34749</t>
+          <t>34828</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29864</t>
+          <t>29831</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30461</t>
+          <t>30515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56844</t>
+          <t>56494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15911</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39617</t>
+          <t>39756</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21980</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48026</t>
+          <t>47685</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>639635</t>
+          <t>638073</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>667654</t>
+          <t>668270</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>658347</t>
+          <t>657025</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>679354</t>
+          <t>679536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1305008</t>
+          <t>1305146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1341330</t>
+          <t>1340629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29436</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55291</t>
+          <t>55320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26316</t>
+          <t>26169</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52326</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62576</t>
+          <t>61736</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99244</t>
+          <t>99527</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34413</t>
+          <t>33170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67204</t>
+          <t>64989</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15147</t>
+          <t>14764</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36155</t>
+          <t>35796</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53941</t>
+          <t>53364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91860</t>
+          <t>92527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>904769</t>
+          <t>908017</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>944920</t>
+          <t>947104</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>951634</t>
+          <t>951963</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>984402</t>
+          <t>983059</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1871160</t>
+          <t>1870144</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1921388</t>
+          <t>1920976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29081</t>
+          <t>29402</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55354</t>
+          <t>59201</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20471</t>
+          <t>19052</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42813</t>
+          <t>42653</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>53147</t>
+          <t>52785</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>88777</t>
+          <t>89328</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28236</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57628</t>
+          <t>58082</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>31531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61755</t>
+          <t>61427</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65914</t>
+          <t>64991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106097</t>
+          <t>107628</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>653308</t>
+          <t>652717</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>691274</t>
+          <t>691044</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>682912</t>
+          <t>684214</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720802</t>
+          <t>721422</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,47 +5337,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>88,04%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>92,83%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1378037</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1348602</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1405184</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>89,79%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>87,87%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>92,75%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1378037</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1348704</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1402251</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>89,79%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>87,88%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38143</t>
+          <t>39931</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68441</t>
+          <t>70259</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49775</t>
+          <t>47859</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>79733</t>
+          <t>80338</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94309</t>
+          <t>95474</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136652</t>
+          <t>139134</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33671</t>
+          <t>34122</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61972</t>
+          <t>61931</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34276</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>63515</t>
+          <t>65223</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>74811</t>
+          <t>74652</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>115748</t>
+          <t>113706</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>825833</t>
+          <t>825154</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>866098</t>
+          <t>866483</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>919421</t>
+          <t>919534</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>960666</t>
+          <t>961874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1761246</t>
+          <t>1761590</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1820076</t>
+          <t>1816923</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6141,42 +6141,42 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>4907</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>12256</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>0,02%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>0,18%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>4907</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>1230</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>12221</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133276</t>
+          <t>134421</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>184942</t>
+          <t>184742</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,82 +6214,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>149481</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>126879</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>177634</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>307143</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>271477</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>346402</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>3,89%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>149481</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>123817</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>179107</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>307143</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>272489</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>344341</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>132254</t>
+          <t>133970</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>186562</t>
+          <t>187468</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>98361</t>
+          <t>101182</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148153</t>
+          <t>148779</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>245064</t>
+          <t>246002</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>316904</t>
+          <t>318570</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3066908</t>
+          <t>3068068</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3142409</t>
+          <t>3140983</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3243288</t>
+          <t>3248578</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3315940</t>
+          <t>3317239</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6337181</t>
+          <t>6340532</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6438399</t>
+          <t>6443625</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19912</t>
+          <t>21473</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,47 +7050,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>26441</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>17221</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>39333</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>26441</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>17551</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>39543</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12066</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31652</t>
+          <t>32337</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>17325</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18378</t>
+          <t>19475</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41775</t>
+          <t>42289</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>628708</t>
+          <t>627857</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>651928</t>
+          <t>652059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>637148</t>
+          <t>636103</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>657450</t>
+          <t>656189</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1272470</t>
+          <t>1273236</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1304110</t>
+          <t>1304806</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25741</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52086</t>
+          <t>49945</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,82 +7584,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>47990</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>35759</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>65307</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>85117</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>66867</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>105200</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>5,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>47990</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>34825</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>62736</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>85117</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>66800</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>105909</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41166</t>
+          <t>40270</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74392</t>
+          <t>71851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>17175</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35827</t>
+          <t>36150</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61932</t>
+          <t>63403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100846</t>
+          <t>100068</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>905531</t>
+          <t>905750</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>946763</t>
+          <t>946218</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>949380</t>
+          <t>946140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>983126</t>
+          <t>981424</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1864752</t>
+          <t>1866706</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1919658</t>
+          <t>1919343</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31488</t>
+          <t>31062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,47 +8153,47 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>20387</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>12649</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>30850</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
           <t>1,62%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>20387</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>12669</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>30449</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>30237</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>55490</t>
+          <t>55325</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10453</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27121</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20945</t>
+          <t>21307</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43658</t>
+          <t>43874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34047</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63073</t>
+          <t>63536</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>704942</t>
+          <t>706415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>730860</t>
+          <t>730835</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>712892</t>
+          <t>714465</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>741048</t>
+          <t>742803</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1428240</t>
+          <t>1428886</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1466091</t>
+          <t>1465915</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>11533</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11481</t>
+          <t>12724</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41841</t>
+          <t>40778</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68766</t>
+          <t>69247</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53659</t>
+          <t>54470</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88740</t>
+          <t>89753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101543</t>
+          <t>102922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146432</t>
+          <t>148124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51059</t>
+          <t>48363</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>81136</t>
+          <t>81881</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43542</t>
+          <t>44189</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72689</t>
+          <t>73043</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>99015</t>
+          <t>102171</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>143370</t>
+          <t>145095</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>791494</t>
+          <t>790776</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>831811</t>
+          <t>834740</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>894434</t>
+          <t>893398</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>938066</t>
+          <t>937388</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1698761</t>
+          <t>1694984</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1762062</t>
+          <t>1760022</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14424</t>
+          <t>15129</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>849</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19820</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100327</t>
+          <t>102353</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>145220</t>
+          <t>147112</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>127672</t>
+          <t>128219</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>180542</t>
+          <t>178209</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>242007</t>
+          <t>243150</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>309059</t>
+          <t>309252</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>133439</t>
+          <t>132057</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>183385</t>
+          <t>181056</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101340</t>
+          <t>100772</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>146890</t>
+          <t>143360</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>246904</t>
+          <t>244818</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>310704</t>
+          <t>309590</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3072144</t>
+          <t>3069557</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3136828</t>
+          <t>3136453</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3222176</t>
+          <t>3228360</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3293097</t>
+          <t>3294311</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6318701</t>
+          <t>6315169</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6408154</t>
+          <t>6406265</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25158</t>
+          <t>28362</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16482</t>
+          <t>18400</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>41515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>36031</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24435</t>
+          <t>26847</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42560</t>
+          <t>46410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>57758</t>
+          <t>64393</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44164</t>
+          <t>52352</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71459</t>
+          <t>81249</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>28133</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,27 +10220,27 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -10255,27 +10255,27 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>23660</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>17600</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34849</t>
+          <t>36413</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>594235</t>
+          <t>644222</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>580837</t>
+          <t>628702</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>605802</t>
+          <t>656641</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>684255</t>
+          <t>689384</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>673129</t>
+          <t>678452</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>694110</t>
+          <t>699593</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1278490</t>
+          <t>1333605</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1259913</t>
+          <t>1315549</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1294749</t>
+          <t>1349433</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -10538,12 +10538,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,67 +10563,67 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>767</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>3789</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>3349</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>7840</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>87171</t>
+          <t>96596</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44515</t>
+          <t>75944</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123386</t>
+          <t>121975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>79981</t>
+          <t>89419</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66957</t>
+          <t>73627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94723</t>
+          <t>106005</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>167151</t>
+          <t>186014</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107440</t>
+          <t>160465</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202854</t>
+          <t>217603</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>35531</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>24516</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46395</t>
+          <t>51255</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27388</t>
+          <t>29687</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>21686</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36961</t>
+          <t>39852</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>57960</t>
+          <t>65219</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36813</t>
+          <t>50418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75563</t>
+          <t>84275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1074106</t>
+          <t>915647</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1031001</t>
+          <t>886491</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1135517</t>
+          <t>937307</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>848949</t>
+          <t>949722</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>831030</t>
+          <t>931323</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>865450</t>
+          <t>968022</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1923056</t>
+          <t>1865369</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1881711</t>
+          <t>1830955</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2005347</t>
+          <t>1898487</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>708</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>708</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75419</t>
+          <t>84519</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58627</t>
+          <t>66970</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93999</t>
+          <t>103426</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>85212</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40559</t>
+          <t>82207</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>115083</t>
+          <t>119944</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>160632</t>
+          <t>184396</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>110139</t>
+          <t>158248</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>196753</t>
+          <t>211613</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>28699</t>
+          <t>31100</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17945</t>
+          <t>19274</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46941</t>
+          <t>50257</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31759</t>
+          <t>30645</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>48841</t>
+          <t>52541</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30563</t>
+          <t>38437</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67486</t>
+          <t>69842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>600562</t>
+          <t>687454</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>577825</t>
+          <t>663156</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>620888</t>
+          <t>707925</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>827348</t>
+          <t>690233</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>790518</t>
+          <t>669851</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>882353</t>
+          <t>707876</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1427910</t>
+          <t>1377687</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1382888</t>
+          <t>1348292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1492303</t>
+          <t>1406605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -11676,12 +11676,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>758</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>131948</t>
+          <t>136982</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110497</t>
+          <t>115816</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155351</t>
+          <t>162308</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>157404</t>
+          <t>165180</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>127224</t>
+          <t>144724</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>181894</t>
+          <t>186925</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>289353</t>
+          <t>302162</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>250355</t>
+          <t>275984</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>323132</t>
+          <t>333917</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>45946</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31546</t>
+          <t>35795</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55697</t>
+          <t>60985</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41002</t>
+          <t>43427</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29984</t>
+          <t>33092</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55371</t>
+          <t>56311</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>82630</t>
+          <t>89374</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>65657</t>
+          <t>72727</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>106631</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>752266</t>
+          <t>804413</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>725877</t>
+          <t>777239</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>774954</t>
+          <t>828915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>891026</t>
+          <t>905339</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>865175</t>
+          <t>881747</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>930507</t>
+          <t>928435</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1643292</t>
+          <t>1709752</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1607076</t>
+          <t>1672966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1689238</t>
+          <t>1740513</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>82,59%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1092430</t>
+          <t>1117253</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1092430</t>
+          <t>1117253</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1092430</t>
+          <t>1117253</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2019261</t>
+          <t>2107315</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2019261</t>
+          <t>2107315</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2019261</t>
+          <t>2107315</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,102 +12235,102 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>12727</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>6660</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>3032</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>12924</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>5995</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2709</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>11574</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>11577</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>6509</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>20990</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>8863</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>4614</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>15312</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>319697</t>
+          <t>346458</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>251315</t>
+          <t>310838</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>367897</t>
+          <t>388363</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>355197</t>
+          <t>390507</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>286828</t>
+          <t>356996</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>398720</t>
+          <t>421883</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>674894</t>
+          <t>736965</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>593810</t>
+          <t>689583</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>748813</t>
+          <t>794351</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>116083</t>
+          <t>129651</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>87735</t>
+          <t>106685</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>143359</t>
+          <t>157664</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>97007</t>
+          <t>103320</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>77954</t>
+          <t>88237</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>115777</t>
+          <t>122501</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>213090</t>
+          <t>232971</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>177030</t>
+          <t>206312</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>248156</t>
+          <t>267697</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3021169</t>
+          <t>3051735</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2964842</t>
+          <t>3006005</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3114091</t>
+          <t>3093338</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3251579</t>
+          <t>3234679</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3200973</t>
+          <t>3198090</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3337930</t>
+          <t>3270758</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6272748</t>
+          <t>6286414</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6190804</t>
+          <t>6224127</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6384041</t>
+          <t>6343195</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3709778</t>
+          <t>3735166</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3709778</t>
+          <t>3735166</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3709778</t>
+          <t>3735166</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7169595</t>
+          <t>7267928</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7169595</t>
+          <t>7267928</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7169595</t>
+          <t>7267928</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
